--- a/data/Фактические затраты по ОР.xlsx
+++ b/data/Фактические затраты по ОР.xlsx
@@ -946,7 +946,7 @@
         <v>13.9</v>
       </c>
       <c r="AF29" t="n">
-        <v>2085</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="30">
@@ -2198,7 +2198,7 @@
         <v>16.8</v>
       </c>
       <c r="AF71" t="n">
-        <v>2016</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="72">
@@ -3155,7 +3155,7 @@
         <v>2.9</v>
       </c>
       <c r="AF105" t="n">
-        <v>2030</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="106">
@@ -3241,13 +3241,13 @@
         <v>7.1</v>
       </c>
       <c r="AD109" t="n">
-        <v>1988</v>
+        <v>2025</v>
       </c>
       <c r="AE109" t="n">
         <v>7.3</v>
       </c>
       <c r="AF109" t="n">
-        <v>2044</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="110">
@@ -3421,7 +3421,7 @@
         <v>17.1</v>
       </c>
       <c r="H115" t="n">
-        <v>2052</v>
+        <v>2025</v>
       </c>
       <c r="K115" t="n">
         <v>2.5</v>
@@ -4094,7 +4094,7 @@
         <v>7.4</v>
       </c>
       <c r="Z136" t="n">
-        <v>2072</v>
+        <v>2025</v>
       </c>
       <c r="AA136" t="n">
         <v>1.6</v>
@@ -4213,7 +4213,7 @@
         <v>4.3</v>
       </c>
       <c r="R140" t="n">
-        <v>1935</v>
+        <v>2025</v>
       </c>
       <c r="S140" t="n">
         <v>18.2</v>
@@ -4531,7 +4531,7 @@
         </is>
       </c>
       <c r="J151" t="n">
-        <v>2085</v>
+        <v>2025</v>
       </c>
       <c r="R151" t="n">
         <v>6359</v>
@@ -5276,7 +5276,7 @@
         <v>16.4</v>
       </c>
       <c r="Z176" t="n">
-        <v>1968</v>
+        <v>2025</v>
       </c>
       <c r="AA176" t="n">
         <v>2.2</v>
@@ -5417,7 +5417,7 @@
         <v>18420</v>
       </c>
       <c r="L180" t="n">
-        <v>1971</v>
+        <v>2025</v>
       </c>
       <c r="N180" t="n">
         <v>3777</v>
@@ -5513,7 +5513,7 @@
         <v>17.5</v>
       </c>
       <c r="Z182" t="n">
-        <v>2100</v>
+        <v>2025</v>
       </c>
       <c r="AC182" t="n">
         <v>0.4</v>
@@ -7237,7 +7237,7 @@
         <v>12.7</v>
       </c>
       <c r="H242" t="n">
-        <v>1905</v>
+        <v>2025</v>
       </c>
       <c r="K242" t="n">
         <v>15</v>
@@ -7373,7 +7373,7 @@
         <v>9.9</v>
       </c>
       <c r="N246" t="n">
-        <v>1980</v>
+        <v>2025</v>
       </c>
       <c r="U246" t="n">
         <v>13.8</v>
@@ -7519,7 +7519,7 @@
         <v>7.1</v>
       </c>
       <c r="X250" t="n">
-        <v>1988</v>
+        <v>2025</v>
       </c>
       <c r="AA250" t="n">
         <v>12.6</v>
@@ -8379,7 +8379,7 @@
         <v>17.1</v>
       </c>
       <c r="R282" t="n">
-        <v>2052</v>
+        <v>2025</v>
       </c>
       <c r="AA282" t="n">
         <v>19.7</v>
@@ -8875,7 +8875,7 @@
         <v>9.6</v>
       </c>
       <c r="L299" t="n">
-        <v>1920</v>
+        <v>2025</v>
       </c>
       <c r="Q299" t="n">
         <v>11.8</v>
@@ -9287,7 +9287,7 @@
         <v>4.3</v>
       </c>
       <c r="X314" t="n">
-        <v>1935</v>
+        <v>2025</v>
       </c>
       <c r="AE314" t="n">
         <v>20.1</v>
@@ -9550,7 +9550,7 @@
         <v>13.2</v>
       </c>
       <c r="R322" t="n">
-        <v>1980</v>
+        <v>2025</v>
       </c>
       <c r="AA322" t="n">
         <v>5.1</v>
@@ -9622,7 +9622,7 @@
         <v>17.4</v>
       </c>
       <c r="AB324" t="n">
-        <v>2088</v>
+        <v>2025</v>
       </c>
       <c r="AE324" t="n">
         <v>47.8</v>
@@ -9685,7 +9685,7 @@
         <v>16.4</v>
       </c>
       <c r="P327" t="n">
-        <v>1968</v>
+        <v>2025</v>
       </c>
       <c r="U327" t="n">
         <v>13.6</v>
@@ -10187,7 +10187,7 @@
         <v>16.5</v>
       </c>
       <c r="H346" t="n">
-        <v>1980</v>
+        <v>2025</v>
       </c>
       <c r="I346" t="n">
         <v>7</v>
@@ -10561,7 +10561,7 @@
         <v>7.5</v>
       </c>
       <c r="Z358" t="n">
-        <v>2100</v>
+        <v>2025</v>
       </c>
       <c r="AE358" t="n">
         <v>49.4</v>
@@ -10971,7 +10971,7 @@
         <v>2.9</v>
       </c>
       <c r="V370" t="n">
-        <v>2030</v>
+        <v>2025</v>
       </c>
       <c r="W370" t="n">
         <v>13.1</v>
@@ -11507,7 +11507,7 @@
         <v>2.9</v>
       </c>
       <c r="AD387" t="n">
-        <v>2030</v>
+        <v>2025</v>
       </c>
       <c r="AE387" t="n">
         <v>25</v>
@@ -11549,7 +11549,7 @@
         <v>6.8</v>
       </c>
       <c r="Z388" t="n">
-        <v>1904</v>
+        <v>2025</v>
       </c>
       <c r="AA388" t="n">
         <v>7.9</v>
@@ -11795,7 +11795,7 @@
         <v>17.4</v>
       </c>
       <c r="AB396" t="n">
-        <v>2088</v>
+        <v>2025</v>
       </c>
       <c r="AE396" t="n">
         <v>25.6</v>
@@ -12086,7 +12086,7 @@
         <v>7.4</v>
       </c>
       <c r="P405" t="n">
-        <v>2072</v>
+        <v>2025</v>
       </c>
       <c r="AE405" t="n">
         <v>16.4</v>
@@ -12271,7 +12271,7 @@
         <v>10.1</v>
       </c>
       <c r="T412" t="n">
-        <v>2020</v>
+        <v>2025</v>
       </c>
       <c r="U412" t="n">
         <v>2.2</v>
